--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171360</v>
+        <v>121171378</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>57720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -848,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546997</v>
+        <v>547093</v>
       </c>
       <c r="R3" t="n">
-        <v>6345402</v>
+        <v>6345474</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,11 +880,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171362</v>
+        <v>121171370</v>
       </c>
       <c r="B4" t="n">
-        <v>58205</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,51 +922,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547049</v>
+        <v>547099</v>
       </c>
       <c r="R4" t="n">
-        <v>6345450</v>
+        <v>6345432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,13 +997,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1039,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171355</v>
+        <v>121171359</v>
       </c>
       <c r="B5" t="n">
-        <v>90707</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,35 +1042,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1088,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547058</v>
+        <v>546992</v>
       </c>
       <c r="R5" t="n">
-        <v>6345475</v>
+        <v>6345410</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171365</v>
+        <v>121171371</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547052</v>
+        <v>547084</v>
       </c>
       <c r="R6" t="n">
-        <v>6345436</v>
+        <v>6345438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171375</v>
+        <v>121171357</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1328,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547102</v>
+        <v>547005</v>
       </c>
       <c r="R7" t="n">
-        <v>6345472</v>
+        <v>6345438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171357</v>
+        <v>121171365</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,7 +1425,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1448,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547005</v>
+        <v>547052</v>
       </c>
       <c r="R8" t="n">
-        <v>6345438</v>
+        <v>6345436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171379</v>
+        <v>121171381</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,7 +1545,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1568,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547090</v>
+        <v>547088</v>
       </c>
       <c r="R9" t="n">
-        <v>6345477</v>
+        <v>6345487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171359</v>
+        <v>121171355</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,35 +1642,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1688,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546992</v>
+        <v>547058</v>
       </c>
       <c r="R10" t="n">
-        <v>6345410</v>
+        <v>6345475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1719,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171361</v>
+        <v>121171362</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>58208</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,47 +1762,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547061</v>
+        <v>547049</v>
       </c>
       <c r="R11" t="n">
-        <v>6345445</v>
+        <v>6345450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,17 +1841,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1879,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171377</v>
+        <v>121171363</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,7 +1905,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1928,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547093</v>
+        <v>547045</v>
       </c>
       <c r="R12" t="n">
-        <v>6345483</v>
+        <v>6345471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171368</v>
+        <v>121171356</v>
       </c>
       <c r="B13" t="n">
-        <v>97025</v>
+        <v>90697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,38 +2002,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547079</v>
+        <v>547068</v>
       </c>
       <c r="R13" t="n">
-        <v>6345400</v>
+        <v>6345467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171354</v>
+        <v>121171377</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547046</v>
+        <v>547093</v>
       </c>
       <c r="R14" t="n">
-        <v>6345478</v>
+        <v>6345483</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171366</v>
+        <v>121171373</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547060</v>
+        <v>547105</v>
       </c>
       <c r="R15" t="n">
-        <v>6345390</v>
+        <v>6345462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171369</v>
+        <v>121171372</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547084</v>
+        <v>547098</v>
       </c>
       <c r="R16" t="n">
-        <v>6345408</v>
+        <v>6345456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171371</v>
+        <v>121171369</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2522,7 +2522,7 @@
         <v>547084</v>
       </c>
       <c r="R17" t="n">
-        <v>6345438</v>
+        <v>6345408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171370</v>
+        <v>121171364</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547099</v>
+        <v>547046</v>
       </c>
       <c r="R18" t="n">
-        <v>6345432</v>
+        <v>6345460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171358</v>
+        <v>121171366</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546976</v>
+        <v>547060</v>
       </c>
       <c r="R19" t="n">
-        <v>6345407</v>
+        <v>6345390</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171363</v>
+        <v>121171361</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547045</v>
+        <v>547061</v>
       </c>
       <c r="R20" t="n">
-        <v>6345471</v>
+        <v>6345445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171378</v>
+        <v>121171354</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,31 +2962,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2995,13 +2999,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547093</v>
+        <v>547046</v>
       </c>
       <c r="R21" t="n">
-        <v>6345474</v>
+        <v>6345478</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3031,6 +3035,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3061,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171372</v>
+        <v>121171379</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,7 +3105,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3110,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547098</v>
+        <v>547090</v>
       </c>
       <c r="R22" t="n">
-        <v>6345456</v>
+        <v>6345477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3181,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171381</v>
+        <v>121171375</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3216,7 +3225,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3230,10 +3239,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547088</v>
+        <v>547102</v>
       </c>
       <c r="R23" t="n">
-        <v>6345487</v>
+        <v>6345472</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3301,10 +3310,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171364</v>
+        <v>121171360</v>
       </c>
       <c r="B24" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3336,7 +3345,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3350,10 +3359,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547046</v>
+        <v>546997</v>
       </c>
       <c r="R24" t="n">
-        <v>6345460</v>
+        <v>6345402</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3421,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171356</v>
+        <v>121171358</v>
       </c>
       <c r="B25" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3433,35 +3442,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3470,10 +3479,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547068</v>
+        <v>546976</v>
       </c>
       <c r="R25" t="n">
-        <v>6345467</v>
+        <v>6345407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,7 +3519,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3541,10 +3550,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171373</v>
+        <v>121171368</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>97035</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3553,47 +3562,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547105</v>
+        <v>547079</v>
       </c>
       <c r="R26" t="n">
-        <v>6345462</v>
+        <v>6345400</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171378</v>
+        <v>121171368</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,42 +815,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547093</v>
+        <v>547079</v>
       </c>
       <c r="R3" t="n">
-        <v>6345474</v>
+        <v>6345400</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +875,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171370</v>
+        <v>121171379</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547099</v>
+        <v>547090</v>
       </c>
       <c r="R4" t="n">
-        <v>6345432</v>
+        <v>6345477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171359</v>
+        <v>121171362</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>58208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,47 +1042,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546992</v>
+        <v>547049</v>
       </c>
       <c r="R5" t="n">
-        <v>6345410</v>
+        <v>6345450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,17 +1121,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171371</v>
+        <v>121171369</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1202,7 +1202,7 @@
         <v>547084</v>
       </c>
       <c r="R6" t="n">
-        <v>6345438</v>
+        <v>6345408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171357</v>
+        <v>121171381</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547005</v>
+        <v>547088</v>
       </c>
       <c r="R7" t="n">
-        <v>6345438</v>
+        <v>6345487</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171365</v>
+        <v>121171357</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547052</v>
+        <v>547005</v>
       </c>
       <c r="R8" t="n">
-        <v>6345436</v>
+        <v>6345438</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171381</v>
+        <v>121171355</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>90717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547088</v>
+        <v>547058</v>
       </c>
       <c r="R9" t="n">
-        <v>6345487</v>
+        <v>6345475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171355</v>
+        <v>121171373</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,35 +1642,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547058</v>
+        <v>547105</v>
       </c>
       <c r="R10" t="n">
-        <v>6345475</v>
+        <v>6345462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171362</v>
+        <v>121171359</v>
       </c>
       <c r="B11" t="n">
-        <v>58208</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,51 +1762,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547049</v>
+        <v>546992</v>
       </c>
       <c r="R11" t="n">
-        <v>6345450</v>
+        <v>6345410</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,13 +1837,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171363</v>
+        <v>121171365</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547045</v>
+        <v>547052</v>
       </c>
       <c r="R12" t="n">
-        <v>6345471</v>
+        <v>6345436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171356</v>
+        <v>121171371</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547068</v>
+        <v>547084</v>
       </c>
       <c r="R13" t="n">
-        <v>6345467</v>
+        <v>6345438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,7 +2110,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171377</v>
+        <v>121171364</v>
       </c>
       <c r="B14" t="n">
         <v>98081</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547093</v>
+        <v>547046</v>
       </c>
       <c r="R14" t="n">
-        <v>6345483</v>
+        <v>6345460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171373</v>
+        <v>121171363</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547105</v>
+        <v>547045</v>
       </c>
       <c r="R15" t="n">
-        <v>6345462</v>
+        <v>6345471</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171369</v>
+        <v>121171358</v>
       </c>
       <c r="B17" t="n">
         <v>98081</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547084</v>
+        <v>546976</v>
       </c>
       <c r="R17" t="n">
-        <v>6345408</v>
+        <v>6345407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171364</v>
+        <v>121171360</v>
       </c>
       <c r="B18" t="n">
         <v>98081</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547046</v>
+        <v>546997</v>
       </c>
       <c r="R18" t="n">
-        <v>6345460</v>
+        <v>6345402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171366</v>
+        <v>121171377</v>
       </c>
       <c r="B19" t="n">
         <v>98081</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547060</v>
+        <v>547093</v>
       </c>
       <c r="R19" t="n">
-        <v>6345390</v>
+        <v>6345483</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2950,7 +2950,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171354</v>
+        <v>121171375</v>
       </c>
       <c r="B21" t="n">
         <v>98081</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547046</v>
+        <v>547102</v>
       </c>
       <c r="R21" t="n">
-        <v>6345478</v>
+        <v>6345472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171379</v>
+        <v>121171354</v>
       </c>
       <c r="B22" t="n">
         <v>98081</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547090</v>
+        <v>547046</v>
       </c>
       <c r="R22" t="n">
-        <v>6345477</v>
+        <v>6345478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171375</v>
+        <v>121171356</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3202,35 +3202,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547102</v>
+        <v>547068</v>
       </c>
       <c r="R23" t="n">
-        <v>6345472</v>
+        <v>6345467</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3310,7 +3310,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171360</v>
+        <v>121171366</v>
       </c>
       <c r="B24" t="n">
         <v>98081</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546997</v>
+        <v>547060</v>
       </c>
       <c r="R24" t="n">
-        <v>6345402</v>
+        <v>6345390</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171358</v>
+        <v>121171370</v>
       </c>
       <c r="B25" t="n">
         <v>98081</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546976</v>
+        <v>547099</v>
       </c>
       <c r="R25" t="n">
-        <v>6345407</v>
+        <v>6345432</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171368</v>
+        <v>121171378</v>
       </c>
       <c r="B26" t="n">
-        <v>97035</v>
+        <v>57720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3566,37 +3566,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547079</v>
+        <v>547093</v>
       </c>
       <c r="R26" t="n">
-        <v>6345400</v>
+        <v>6345474</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3626,11 +3631,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lite</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -3190,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171356</v>
+        <v>121171366</v>
       </c>
       <c r="B23" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3202,25 +3202,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547068</v>
+        <v>547060</v>
       </c>
       <c r="R23" t="n">
-        <v>6345467</v>
+        <v>6345390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3310,7 +3310,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171366</v>
+        <v>121171370</v>
       </c>
       <c r="B24" t="n">
         <v>98081</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547060</v>
+        <v>547099</v>
       </c>
       <c r="R24" t="n">
-        <v>6345390</v>
+        <v>6345432</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171370</v>
+        <v>121171356</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3442,35 +3442,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547099</v>
+        <v>547068</v>
       </c>
       <c r="R25" t="n">
-        <v>6345432</v>
+        <v>6345467</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171368</v>
+        <v>121171356</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,38 +811,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547079</v>
+        <v>547068</v>
       </c>
       <c r="R3" t="n">
-        <v>6345400</v>
+        <v>6345467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171379</v>
+        <v>121171360</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +954,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547090</v>
+        <v>546997</v>
       </c>
       <c r="R4" t="n">
-        <v>6345477</v>
+        <v>6345402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171362</v>
+        <v>121171377</v>
       </c>
       <c r="B5" t="n">
-        <v>58208</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,51 +1051,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547049</v>
+        <v>547093</v>
       </c>
       <c r="R5" t="n">
-        <v>6345450</v>
+        <v>6345483</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,13 +1126,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171369</v>
+        <v>121171373</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547084</v>
+        <v>547105</v>
       </c>
       <c r="R6" t="n">
-        <v>6345408</v>
+        <v>6345462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1248,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171381</v>
+        <v>121171366</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1314,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547088</v>
+        <v>547060</v>
       </c>
       <c r="R7" t="n">
-        <v>6345487</v>
+        <v>6345390</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171357</v>
+        <v>121171381</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,7 +1434,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1439,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547005</v>
+        <v>547088</v>
       </c>
       <c r="R8" t="n">
-        <v>6345438</v>
+        <v>6345487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171355</v>
+        <v>121171358</v>
       </c>
       <c r="B9" t="n">
-        <v>90717</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,35 +1531,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1559,10 +1568,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547058</v>
+        <v>546976</v>
       </c>
       <c r="R9" t="n">
-        <v>6345475</v>
+        <v>6345407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1608,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171373</v>
+        <v>121171379</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,7 +1674,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547105</v>
+        <v>547090</v>
       </c>
       <c r="R10" t="n">
-        <v>6345462</v>
+        <v>6345477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171359</v>
+        <v>121171370</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,7 +1794,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1799,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546992</v>
+        <v>547099</v>
       </c>
       <c r="R11" t="n">
-        <v>6345410</v>
+        <v>6345432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1870,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171365</v>
+        <v>121171354</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,7 +1914,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547052</v>
+        <v>547046</v>
       </c>
       <c r="R12" t="n">
-        <v>6345436</v>
+        <v>6345478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171371</v>
+        <v>121171375</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2025,7 +2034,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2039,10 +2048,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547084</v>
+        <v>547102</v>
       </c>
       <c r="R13" t="n">
-        <v>6345438</v>
+        <v>6345472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2088,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171364</v>
+        <v>121171361</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,7 +2154,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2168,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547046</v>
+        <v>547061</v>
       </c>
       <c r="R14" t="n">
-        <v>6345460</v>
+        <v>6345445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,10 +2239,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171363</v>
+        <v>121171364</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2265,7 +2274,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2279,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547045</v>
+        <v>547046</v>
       </c>
       <c r="R15" t="n">
-        <v>6345471</v>
+        <v>6345460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171372</v>
+        <v>121171362</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>58208</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,47 +2371,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547098</v>
+        <v>547049</v>
       </c>
       <c r="R16" t="n">
-        <v>6345456</v>
+        <v>6345450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,17 +2450,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171358</v>
+        <v>121171357</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,7 +2514,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2519,10 +2528,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546976</v>
+        <v>547005</v>
       </c>
       <c r="R17" t="n">
-        <v>6345407</v>
+        <v>6345438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171360</v>
+        <v>121171368</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>97048</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,47 +2611,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546997</v>
+        <v>547079</v>
       </c>
       <c r="R18" t="n">
-        <v>6345402</v>
+        <v>6345400</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171377</v>
+        <v>121171369</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547093</v>
+        <v>547084</v>
       </c>
       <c r="R19" t="n">
-        <v>6345483</v>
+        <v>6345408</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171361</v>
+        <v>121171359</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547061</v>
+        <v>546992</v>
       </c>
       <c r="R20" t="n">
-        <v>6345445</v>
+        <v>6345410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171375</v>
+        <v>121171372</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547102</v>
+        <v>547098</v>
       </c>
       <c r="R21" t="n">
-        <v>6345472</v>
+        <v>6345456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171354</v>
+        <v>121171365</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547046</v>
+        <v>547052</v>
       </c>
       <c r="R22" t="n">
-        <v>6345478</v>
+        <v>6345436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171366</v>
+        <v>121171363</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547060</v>
+        <v>547045</v>
       </c>
       <c r="R23" t="n">
-        <v>6345390</v>
+        <v>6345471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171370</v>
+        <v>121171371</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547099</v>
+        <v>547084</v>
       </c>
       <c r="R24" t="n">
-        <v>6345432</v>
+        <v>6345438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171356</v>
+        <v>121171355</v>
       </c>
       <c r="B25" t="n">
-        <v>90697</v>
+        <v>90729</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547068</v>
+        <v>547058</v>
       </c>
       <c r="R25" t="n">
-        <v>6345467</v>
+        <v>6345475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171356</v>
+        <v>121171372</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547068</v>
+        <v>547098</v>
       </c>
       <c r="R3" t="n">
-        <v>6345467</v>
+        <v>6345456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171360</v>
+        <v>121171358</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546997</v>
+        <v>546976</v>
       </c>
       <c r="R4" t="n">
-        <v>6345402</v>
+        <v>6345407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171377</v>
+        <v>121171378</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>57720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,35 +1051,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1087,10 @@
         <v>547093</v>
       </c>
       <c r="R5" t="n">
-        <v>6345483</v>
+        <v>6345474</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,11 +1120,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171373</v>
+        <v>121171375</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547105</v>
+        <v>547102</v>
       </c>
       <c r="R6" t="n">
-        <v>6345462</v>
+        <v>6345472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171366</v>
+        <v>121171355</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>90730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1319,7 +1310,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1328,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547060</v>
+        <v>547058</v>
       </c>
       <c r="R7" t="n">
-        <v>6345390</v>
+        <v>6345475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1359,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171381</v>
+        <v>121171377</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,7 +1425,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1448,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547088</v>
+        <v>547093</v>
       </c>
       <c r="R8" t="n">
-        <v>6345487</v>
+        <v>6345483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171358</v>
+        <v>121171361</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,7 +1545,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1568,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546976</v>
+        <v>547061</v>
       </c>
       <c r="R9" t="n">
-        <v>6345407</v>
+        <v>6345445</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171379</v>
+        <v>121171357</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,7 +1665,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1688,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547090</v>
+        <v>547005</v>
       </c>
       <c r="R10" t="n">
-        <v>6345477</v>
+        <v>6345438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,7 +1753,7 @@
         <v>121171370</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1879,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171354</v>
+        <v>121171362</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>58208</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,47 +1882,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547046</v>
+        <v>547049</v>
       </c>
       <c r="R12" t="n">
-        <v>6345478</v>
+        <v>6345450</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,17 +1961,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1999,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171375</v>
+        <v>121171356</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,35 +2002,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2048,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547102</v>
+        <v>547068</v>
       </c>
       <c r="R13" t="n">
-        <v>6345472</v>
+        <v>6345467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2088,7 +2079,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171361</v>
+        <v>121171364</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2154,7 +2145,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2168,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547061</v>
+        <v>547046</v>
       </c>
       <c r="R14" t="n">
-        <v>6345445</v>
+        <v>6345460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2239,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171364</v>
+        <v>121171359</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2274,7 +2265,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547046</v>
+        <v>546992</v>
       </c>
       <c r="R15" t="n">
-        <v>6345460</v>
+        <v>6345410</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2359,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171362</v>
+        <v>121171365</v>
       </c>
       <c r="B16" t="n">
-        <v>58208</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,51 +2362,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547049</v>
+        <v>547052</v>
       </c>
       <c r="R16" t="n">
-        <v>6345450</v>
+        <v>6345436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2450,13 +2437,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2479,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171357</v>
+        <v>121171354</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2514,7 +2505,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2528,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547005</v>
+        <v>547046</v>
       </c>
       <c r="R17" t="n">
-        <v>6345438</v>
+        <v>6345478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2599,10 +2590,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171368</v>
+        <v>121171360</v>
       </c>
       <c r="B18" t="n">
-        <v>97048</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,38 +2602,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547079</v>
+        <v>546997</v>
       </c>
       <c r="R18" t="n">
-        <v>6345400</v>
+        <v>6345402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,7 +2713,7 @@
         <v>121171369</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171359</v>
+        <v>121171379</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546992</v>
+        <v>547090</v>
       </c>
       <c r="R20" t="n">
-        <v>6345410</v>
+        <v>6345477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171372</v>
+        <v>121171363</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547098</v>
+        <v>547045</v>
       </c>
       <c r="R21" t="n">
-        <v>6345456</v>
+        <v>6345471</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171365</v>
+        <v>121171366</v>
       </c>
       <c r="B22" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547052</v>
+        <v>547060</v>
       </c>
       <c r="R22" t="n">
-        <v>6345436</v>
+        <v>6345390</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3190,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171363</v>
+        <v>121171373</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547045</v>
+        <v>547105</v>
       </c>
       <c r="R23" t="n">
-        <v>6345471</v>
+        <v>6345462</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171371</v>
+        <v>121171381</v>
       </c>
       <c r="B24" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547084</v>
+        <v>547088</v>
       </c>
       <c r="R24" t="n">
-        <v>6345438</v>
+        <v>6345487</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171355</v>
+        <v>121171371</v>
       </c>
       <c r="B25" t="n">
-        <v>90729</v>
+        <v>98095</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3442,35 +3442,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547058</v>
+        <v>547084</v>
       </c>
       <c r="R25" t="n">
-        <v>6345475</v>
+        <v>6345438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171378</v>
+        <v>121171368</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>97049</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3566,42 +3566,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547093</v>
+        <v>547079</v>
       </c>
       <c r="R26" t="n">
-        <v>6345474</v>
+        <v>6345400</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3631,6 +3626,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>121171372</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171358</v>
+        <v>121171366</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546976</v>
+        <v>547060</v>
       </c>
       <c r="R4" t="n">
-        <v>6345407</v>
+        <v>6345390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171378</v>
+        <v>121171363</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,31 +1051,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547093</v>
+        <v>547045</v>
       </c>
       <c r="R5" t="n">
-        <v>6345474</v>
+        <v>6345471</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,6 +1124,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171375</v>
+        <v>121171364</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547102</v>
+        <v>547046</v>
       </c>
       <c r="R6" t="n">
-        <v>6345472</v>
+        <v>6345460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1270,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171355</v>
+        <v>121171358</v>
       </c>
       <c r="B7" t="n">
-        <v>90730</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,35 +1291,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547058</v>
+        <v>546976</v>
       </c>
       <c r="R7" t="n">
-        <v>6345475</v>
+        <v>6345407</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1368,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171377</v>
+        <v>121171371</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,7 +1434,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1439,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547093</v>
+        <v>547084</v>
       </c>
       <c r="R8" t="n">
-        <v>6345483</v>
+        <v>6345438</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1488,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171361</v>
+        <v>121171357</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,7 +1554,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1559,10 +1568,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547061</v>
+        <v>547005</v>
       </c>
       <c r="R9" t="n">
-        <v>6345445</v>
+        <v>6345438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171357</v>
+        <v>121171362</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>58211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,47 +1651,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547005</v>
+        <v>547049</v>
       </c>
       <c r="R10" t="n">
-        <v>6345438</v>
+        <v>6345450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,17 +1730,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171370</v>
+        <v>121171356</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,35 +1771,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1799,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547099</v>
+        <v>547068</v>
       </c>
       <c r="R11" t="n">
-        <v>6345432</v>
+        <v>6345467</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,7 +1848,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171362</v>
+        <v>121171354</v>
       </c>
       <c r="B12" t="n">
-        <v>58208</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,51 +1891,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547049</v>
+        <v>547046</v>
       </c>
       <c r="R12" t="n">
-        <v>6345450</v>
+        <v>6345478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1961,13 +1966,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1990,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171356</v>
+        <v>121171359</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,35 +2011,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2039,10 +2048,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547068</v>
+        <v>546992</v>
       </c>
       <c r="R13" t="n">
-        <v>6345467</v>
+        <v>6345410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2088,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171364</v>
+        <v>121171368</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>97052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2122,47 +2131,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547046</v>
+        <v>547079</v>
       </c>
       <c r="R14" t="n">
-        <v>6345460</v>
+        <v>6345400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171359</v>
+        <v>121171375</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546992</v>
+        <v>547102</v>
       </c>
       <c r="R15" t="n">
-        <v>6345410</v>
+        <v>6345472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171365</v>
+        <v>121171370</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547052</v>
+        <v>547099</v>
       </c>
       <c r="R16" t="n">
-        <v>6345436</v>
+        <v>6345432</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171354</v>
+        <v>121171378</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>57723</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,35 +2482,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2519,13 +2515,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547046</v>
+        <v>547093</v>
       </c>
       <c r="R17" t="n">
-        <v>6345478</v>
+        <v>6345474</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2555,11 +2551,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171360</v>
+        <v>121171373</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,7 +2616,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2639,10 +2630,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546997</v>
+        <v>547105</v>
       </c>
       <c r="R18" t="n">
-        <v>6345402</v>
+        <v>6345462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171369</v>
+        <v>121171355</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>90733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2722,35 +2713,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2759,10 +2750,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547084</v>
+        <v>547058</v>
       </c>
       <c r="R19" t="n">
-        <v>6345408</v>
+        <v>6345475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2790,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2830,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171379</v>
+        <v>121171365</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2856,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2879,10 +2870,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547090</v>
+        <v>547052</v>
       </c>
       <c r="R20" t="n">
-        <v>6345477</v>
+        <v>6345436</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171363</v>
+        <v>121171360</v>
       </c>
       <c r="B21" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2985,7 +2976,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2999,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547045</v>
+        <v>546997</v>
       </c>
       <c r="R21" t="n">
-        <v>6345471</v>
+        <v>6345402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,10 +3061,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171366</v>
+        <v>121171377</v>
       </c>
       <c r="B22" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3105,7 +3096,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3119,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547060</v>
+        <v>547093</v>
       </c>
       <c r="R22" t="n">
-        <v>6345390</v>
+        <v>6345483</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3150,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3190,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171373</v>
+        <v>121171381</v>
       </c>
       <c r="B23" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3225,7 +3216,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3239,10 +3230,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547105</v>
+        <v>547088</v>
       </c>
       <c r="R23" t="n">
-        <v>6345462</v>
+        <v>6345487</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3310,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171381</v>
+        <v>121171369</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3345,7 +3336,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3359,10 +3350,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547088</v>
+        <v>547084</v>
       </c>
       <c r="R24" t="n">
-        <v>6345487</v>
+        <v>6345408</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,7 +3390,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,10 +3421,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171371</v>
+        <v>121171379</v>
       </c>
       <c r="B25" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,7 +3456,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3479,10 +3470,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547084</v>
+        <v>547090</v>
       </c>
       <c r="R25" t="n">
-        <v>6345438</v>
+        <v>6345477</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3519,7 +3510,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,10 +3541,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171368</v>
+        <v>121171361</v>
       </c>
       <c r="B26" t="n">
-        <v>97049</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3562,38 +3553,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547079</v>
+        <v>547061</v>
       </c>
       <c r="R26" t="n">
-        <v>6345400</v>
+        <v>6345445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171372</v>
+        <v>121171364</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547098</v>
+        <v>547046</v>
       </c>
       <c r="R3" t="n">
-        <v>6345456</v>
+        <v>6345460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171366</v>
+        <v>121171368</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,47 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547060</v>
+        <v>547079</v>
       </c>
       <c r="R4" t="n">
-        <v>6345390</v>
+        <v>6345400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171363</v>
+        <v>121171379</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1074,7 +1065,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1088,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547045</v>
+        <v>547090</v>
       </c>
       <c r="R5" t="n">
-        <v>6345471</v>
+        <v>6345477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171364</v>
+        <v>121171356</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1199,7 +1190,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547046</v>
+        <v>547068</v>
       </c>
       <c r="R6" t="n">
-        <v>6345460</v>
+        <v>6345467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171358</v>
+        <v>121171377</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1314,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1328,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546976</v>
+        <v>547093</v>
       </c>
       <c r="R7" t="n">
-        <v>6345407</v>
+        <v>6345483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,7 +1390,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171371</v>
+        <v>121171381</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1434,7 +1425,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1448,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547084</v>
+        <v>547088</v>
       </c>
       <c r="R8" t="n">
-        <v>6345438</v>
+        <v>6345487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1479,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171357</v>
+        <v>121171362</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>58211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,47 +1522,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547005</v>
+        <v>547049</v>
       </c>
       <c r="R9" t="n">
-        <v>6345438</v>
+        <v>6345450</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,17 +1601,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171362</v>
+        <v>121171365</v>
       </c>
       <c r="B10" t="n">
-        <v>58211</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,51 +1642,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547049</v>
+        <v>547052</v>
       </c>
       <c r="R10" t="n">
-        <v>6345450</v>
+        <v>6345436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,13 +1717,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171356</v>
+        <v>121171366</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1762,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1799,7 +1790,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1808,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547068</v>
+        <v>547060</v>
       </c>
       <c r="R11" t="n">
-        <v>6345467</v>
+        <v>6345390</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,7 +1839,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,7 +1870,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171354</v>
+        <v>121171370</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1914,7 +1905,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1928,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547046</v>
+        <v>547099</v>
       </c>
       <c r="R12" t="n">
-        <v>6345478</v>
+        <v>6345432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,7 +1990,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171359</v>
+        <v>121171357</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -2034,7 +2025,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2048,10 +2039,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546992</v>
+        <v>547005</v>
       </c>
       <c r="R13" t="n">
-        <v>6345410</v>
+        <v>6345438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2119,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171368</v>
+        <v>121171359</v>
       </c>
       <c r="B14" t="n">
-        <v>97052</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,38 +2122,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547079</v>
+        <v>546992</v>
       </c>
       <c r="R14" t="n">
-        <v>6345400</v>
+        <v>6345410</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171375</v>
+        <v>121171355</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>90733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,35 +2242,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547102</v>
+        <v>547058</v>
       </c>
       <c r="R15" t="n">
-        <v>6345472</v>
+        <v>6345475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171370</v>
+        <v>121171369</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547099</v>
+        <v>547084</v>
       </c>
       <c r="R16" t="n">
-        <v>6345432</v>
+        <v>6345408</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171378</v>
+        <v>121171371</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,31 +2482,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2515,13 +2519,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547093</v>
+        <v>547084</v>
       </c>
       <c r="R17" t="n">
-        <v>6345474</v>
+        <v>6345438</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,6 +2555,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,7 +2590,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171373</v>
+        <v>121171372</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2616,7 +2625,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2630,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547105</v>
+        <v>547098</v>
       </c>
       <c r="R18" t="n">
-        <v>6345462</v>
+        <v>6345456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2701,10 +2710,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171355</v>
+        <v>121171375</v>
       </c>
       <c r="B19" t="n">
-        <v>90733</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,35 +2722,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2750,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547058</v>
+        <v>547102</v>
       </c>
       <c r="R19" t="n">
-        <v>6345475</v>
+        <v>6345472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,7 +2799,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,7 +2830,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171365</v>
+        <v>121171361</v>
       </c>
       <c r="B20" t="n">
         <v>98098</v>
@@ -2870,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547052</v>
+        <v>547061</v>
       </c>
       <c r="R20" t="n">
-        <v>6345436</v>
+        <v>6345445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3061,7 +3070,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171377</v>
+        <v>121171363</v>
       </c>
       <c r="B22" t="n">
         <v>98098</v>
@@ -3096,7 +3105,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3110,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547093</v>
+        <v>547045</v>
       </c>
       <c r="R22" t="n">
-        <v>6345483</v>
+        <v>6345471</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3181,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171381</v>
+        <v>121171378</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>57723</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3193,35 +3202,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3230,13 +3235,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547088</v>
+        <v>547093</v>
       </c>
       <c r="R23" t="n">
-        <v>6345487</v>
+        <v>6345474</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3266,11 +3271,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,7 +3301,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171369</v>
+        <v>121171373</v>
       </c>
       <c r="B24" t="n">
         <v>98098</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547084</v>
+        <v>547105</v>
       </c>
       <c r="R24" t="n">
-        <v>6345408</v>
+        <v>6345462</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3421,7 +3421,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171379</v>
+        <v>121171354</v>
       </c>
       <c r="B25" t="n">
         <v>98098</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547090</v>
+        <v>547046</v>
       </c>
       <c r="R25" t="n">
-        <v>6345477</v>
+        <v>6345478</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171361</v>
+        <v>121171358</v>
       </c>
       <c r="B26" t="n">
         <v>98098</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547061</v>
+        <v>546976</v>
       </c>
       <c r="R26" t="n">
-        <v>6345445</v>
+        <v>6345407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171364</v>
+        <v>121171378</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>57724</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -848,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547046</v>
+        <v>547093</v>
       </c>
       <c r="R3" t="n">
-        <v>6345460</v>
+        <v>6345474</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,11 +880,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171368</v>
+        <v>121171359</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +922,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547079</v>
+        <v>546992</v>
       </c>
       <c r="R4" t="n">
-        <v>6345400</v>
+        <v>6345410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171379</v>
+        <v>121171355</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>90739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1042,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547090</v>
+        <v>547058</v>
       </c>
       <c r="R5" t="n">
-        <v>6345477</v>
+        <v>6345475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171356</v>
+        <v>121171377</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,35 +1162,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547068</v>
+        <v>547093</v>
       </c>
       <c r="R6" t="n">
-        <v>6345467</v>
+        <v>6345483</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171377</v>
+        <v>121171362</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>58212</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,47 +1282,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547093</v>
+        <v>547049</v>
       </c>
       <c r="R7" t="n">
-        <v>6345483</v>
+        <v>6345450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,17 +1361,13 @@
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171381</v>
+        <v>121171358</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547088</v>
+        <v>546976</v>
       </c>
       <c r="R8" t="n">
-        <v>6345487</v>
+        <v>6345407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171362</v>
+        <v>121171369</v>
       </c>
       <c r="B9" t="n">
-        <v>58211</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,51 +1522,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547049</v>
+        <v>547084</v>
       </c>
       <c r="R9" t="n">
-        <v>6345450</v>
+        <v>6345408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,13 +1597,17 @@
           <t>2024-05-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 70 årig barrskogsdel</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171365</v>
+        <v>121171364</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547052</v>
+        <v>547046</v>
       </c>
       <c r="R10" t="n">
-        <v>6345436</v>
+        <v>6345460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171366</v>
+        <v>121171381</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547060</v>
+        <v>547088</v>
       </c>
       <c r="R11" t="n">
-        <v>6345390</v>
+        <v>6345487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171370</v>
+        <v>121171373</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547099</v>
+        <v>547105</v>
       </c>
       <c r="R12" t="n">
-        <v>6345432</v>
+        <v>6345462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
         <v>121171357</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171359</v>
+        <v>121171379</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546992</v>
+        <v>547090</v>
       </c>
       <c r="R14" t="n">
-        <v>6345410</v>
+        <v>6345477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171355</v>
+        <v>121171361</v>
       </c>
       <c r="B15" t="n">
-        <v>90733</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,35 +2242,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547058</v>
+        <v>547061</v>
       </c>
       <c r="R15" t="n">
-        <v>6345475</v>
+        <v>6345445</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171369</v>
+        <v>121171370</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547084</v>
+        <v>547099</v>
       </c>
       <c r="R16" t="n">
-        <v>6345408</v>
+        <v>6345432</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171371</v>
+        <v>121171368</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>97058</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,47 +2482,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547084</v>
+        <v>547079</v>
       </c>
       <c r="R17" t="n">
-        <v>6345438</v>
+        <v>6345400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,7 +2550,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171372</v>
+        <v>121171360</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,7 +2616,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2639,10 +2630,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547098</v>
+        <v>546997</v>
       </c>
       <c r="R18" t="n">
-        <v>6345456</v>
+        <v>6345402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171375</v>
+        <v>121171365</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2759,10 +2750,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547102</v>
+        <v>547052</v>
       </c>
       <c r="R19" t="n">
-        <v>6345472</v>
+        <v>6345436</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2830,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171361</v>
+        <v>121171366</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2856,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2879,10 +2870,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547061</v>
+        <v>547060</v>
       </c>
       <c r="R20" t="n">
-        <v>6345445</v>
+        <v>6345390</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2919,7 +2910,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2950,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171360</v>
+        <v>121171371</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2985,7 +2976,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2999,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546997</v>
+        <v>547084</v>
       </c>
       <c r="R21" t="n">
-        <v>6345402</v>
+        <v>6345438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,7 +3030,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3061,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171363</v>
+        <v>121171356</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3082,35 +3073,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3119,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547045</v>
+        <v>547068</v>
       </c>
       <c r="R22" t="n">
-        <v>6345471</v>
+        <v>6345467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3150,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3190,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171378</v>
+        <v>121171363</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3202,31 +3193,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3235,13 +3230,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547093</v>
+        <v>547045</v>
       </c>
       <c r="R23" t="n">
-        <v>6345474</v>
+        <v>6345471</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3271,6 +3266,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171373</v>
+        <v>121171372</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547105</v>
+        <v>547098</v>
       </c>
       <c r="R24" t="n">
-        <v>6345462</v>
+        <v>6345456</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171354</v>
+        <v>121171375</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547046</v>
+        <v>547102</v>
       </c>
       <c r="R25" t="n">
-        <v>6345478</v>
+        <v>6345472</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171358</v>
+        <v>121171354</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546976</v>
+        <v>547046</v>
       </c>
       <c r="R26" t="n">
-        <v>6345407</v>
+        <v>6345478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109462807</v>
+        <v>121171356</v>
       </c>
       <c r="B2" t="n">
-        <v>56595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Älmten, Sm</t>
+          <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547066</v>
+        <v>547068</v>
       </c>
       <c r="R2" t="n">
-        <v>6345437</v>
+        <v>6345467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:06</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:06</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +774,58 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Gustafsson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171378</v>
+        <v>121171355</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547093</v>
+        <v>547058</v>
       </c>
       <c r="R3" t="n">
-        <v>6345474</v>
+        <v>6345475</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,62 +905,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171359</v>
+        <v>109462807</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gällingsbotrakten, Sm</t>
+          <t>N Älmten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546992</v>
+        <v>547066</v>
       </c>
       <c r="R4" t="n">
-        <v>6345410</v>
+        <v>6345437</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,17 +982,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,31 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Fredrik Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171355</v>
+        <v>109462799</v>
       </c>
       <c r="B5" t="n">
-        <v>90739</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>102932</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,24 +1057,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gällingsbotrakten, Sm</t>
+          <t>Älmten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547058</v>
+        <v>547121</v>
       </c>
       <c r="R5" t="n">
-        <v>6345475</v>
+        <v>6345379</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,17 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,63 +1135,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Fredrik Gustafsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Fredrik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171377</v>
+        <v>121171378</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1202,10 +1190,10 @@
         <v>547093</v>
       </c>
       <c r="R6" t="n">
-        <v>6345483</v>
+        <v>6345474</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,11 +1223,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1256,7 @@
         <v>121171362</v>
       </c>
       <c r="B7" t="n">
-        <v>58212</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,15 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121171358</v>
+        <v>121171354</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1398,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1439,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546976</v>
+        <v>547046</v>
       </c>
       <c r="R8" t="n">
-        <v>6345407</v>
+        <v>6345478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,15 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121171369</v>
+        <v>121171357</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1513,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1559,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547084</v>
+        <v>547005</v>
       </c>
       <c r="R9" t="n">
-        <v>6345408</v>
+        <v>6345438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1567,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,15 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121171364</v>
+        <v>121171358</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1628,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547046</v>
+        <v>546976</v>
       </c>
       <c r="R10" t="n">
-        <v>6345460</v>
+        <v>6345407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,15 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121171381</v>
+        <v>121171359</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1743,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1799,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547088</v>
+        <v>546992</v>
       </c>
       <c r="R11" t="n">
-        <v>6345487</v>
+        <v>6345410</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1870,15 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121171373</v>
+        <v>121171360</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1858,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1872,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547105</v>
+        <v>546997</v>
       </c>
       <c r="R12" t="n">
-        <v>6345462</v>
+        <v>6345402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,15 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121171357</v>
+        <v>121171361</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +1973,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2039,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547005</v>
+        <v>547061</v>
       </c>
       <c r="R13" t="n">
-        <v>6345438</v>
+        <v>6345445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,15 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121171379</v>
+        <v>121171363</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2088,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547090</v>
+        <v>547045</v>
       </c>
       <c r="R14" t="n">
-        <v>6345477</v>
+        <v>6345471</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,15 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121171361</v>
+        <v>121171364</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2203,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2279,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547061</v>
+        <v>547046</v>
       </c>
       <c r="R15" t="n">
-        <v>6345445</v>
+        <v>6345460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,15 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121171370</v>
+        <v>121171365</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2318,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2399,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547099</v>
+        <v>547052</v>
       </c>
       <c r="R16" t="n">
-        <v>6345432</v>
+        <v>6345436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2470,50 +2403,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121171368</v>
+        <v>121171366</v>
       </c>
       <c r="B17" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547079</v>
+        <v>547060</v>
       </c>
       <c r="R17" t="n">
-        <v>6345400</v>
+        <v>6345390</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,7 +2487,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,15 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121171360</v>
+        <v>121171369</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,10 +2562,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546997</v>
+        <v>547084</v>
       </c>
       <c r="R18" t="n">
-        <v>6345402</v>
+        <v>6345408</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2670,7 +2602,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 årig barrskog</t>
+          <t>Ca 70 årig barrskogsdel</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,15 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121171365</v>
+        <v>121171370</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2663,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2750,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547052</v>
+        <v>547099</v>
       </c>
       <c r="R19" t="n">
-        <v>6345436</v>
+        <v>6345432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2821,15 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121171366</v>
+        <v>121171371</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2778,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2870,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547060</v>
+        <v>547084</v>
       </c>
       <c r="R20" t="n">
-        <v>6345390</v>
+        <v>6345438</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2910,7 +2832,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel</t>
+          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2941,15 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121171371</v>
+        <v>121171372</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2976,7 +2893,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2990,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547084</v>
+        <v>547098</v>
       </c>
       <c r="R21" t="n">
-        <v>6345438</v>
+        <v>6345456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3030,7 +2947,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 70 årig barrskogsdel, gräns mot minst 120 årig barrskog</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3061,47 +2978,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121171356</v>
+        <v>121171373</v>
       </c>
       <c r="B22" t="n">
-        <v>90719</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3110,10 +3022,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547068</v>
+        <v>547105</v>
       </c>
       <c r="R22" t="n">
-        <v>6345467</v>
+        <v>6345462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,7 +3062,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Minst 120 årig barrskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,15 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121171363</v>
+        <v>121171374</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3216,7 +3123,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3230,10 +3137,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547045</v>
+        <v>547108</v>
       </c>
       <c r="R23" t="n">
-        <v>6345471</v>
+        <v>6345472</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3301,15 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121171372</v>
+        <v>121171375</v>
       </c>
       <c r="B24" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3238,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3350,10 +3252,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547098</v>
+        <v>547102</v>
       </c>
       <c r="R24" t="n">
-        <v>6345456</v>
+        <v>6345472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3421,15 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121171375</v>
+        <v>121171376</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3456,7 +3353,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3470,10 +3367,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547102</v>
+        <v>547101</v>
       </c>
       <c r="R25" t="n">
-        <v>6345472</v>
+        <v>6345487</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,15 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121171354</v>
+        <v>121171377</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3576,7 +3468,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3590,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547046</v>
+        <v>547093</v>
       </c>
       <c r="R26" t="n">
-        <v>6345478</v>
+        <v>6345483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3654,6 +3546,342 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121171379</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547090</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6345477</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121171381</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547088</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6345487</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 120 årig barrskog</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121171368</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547079</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6345400</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 15095-2024 artfynd.xlsx
+++ b/artfynd/A 15095-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171355</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109462807</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109462799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171378</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171362</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171354</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1595,6 +1635,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171357</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171358</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171359</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171360</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2055,6 +2115,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171361</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171363</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2285,6 +2355,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171364</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2400,6 +2475,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171365</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2515,6 +2595,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171366</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171369</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2745,6 +2835,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171370</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2860,6 +2955,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171371</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2975,6 +3075,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171372</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3090,6 +3195,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171373</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3205,6 +3315,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171374</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3320,6 +3435,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171375</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3435,6 +3555,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171376</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3550,6 +3675,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171377</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3665,6 +3795,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171379</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3780,6 +3915,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171381</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3886,8 +4026,43 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>